--- a/data/trans_orig/P58-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P58-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su lugar de nacimiento en 2007</t>
+          <t>Población según su lugar de nacimiento en 2007 (tasa de respuesta: 99,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23688</t>
+          <t>25120</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52805</t>
+          <t>51981</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28406</t>
+          <t>28721</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>58939</t>
+          <t>57864</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>62600</t>
+          <t>60034</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>105456</t>
+          <t>102057</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,61%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16738</t>
+          <t>17056</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42815</t>
+          <t>42863</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14019</t>
+          <t>14351</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32846</t>
+          <t>32828</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35188</t>
+          <t>37126</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>68960</t>
+          <t>67922</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>407886</t>
+          <t>409799</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>445412</t>
+          <t>444398</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>385243</t>
+          <t>385406</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>420209</t>
+          <t>418509</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>802695</t>
+          <t>806057</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>854049</t>
+          <t>857963</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>89,23%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>33148</t>
+          <t>32757</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>65883</t>
+          <t>65013</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>50809</t>
+          <t>52844</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>91342</t>
+          <t>90424</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>92065</t>
+          <t>95779</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>145587</t>
+          <t>142969</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,5%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>62028</t>
+          <t>59386</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>101573</t>
+          <t>103879</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>41096</t>
+          <t>41123</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>70586</t>
+          <t>71045</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>107715</t>
+          <t>109466</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>160684</t>
+          <t>163923</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>12,04%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>580980</t>
+          <t>581060</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>630559</t>
+          <t>630776</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>79,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>478044</t>
+          <t>478526</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>522444</t>
+          <t>523406</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1075690</t>
+          <t>1074695</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1143724</t>
+          <t>1142042</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>83,91%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>32390</t>
+          <t>32990</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>64906</t>
+          <t>64874</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>47827</t>
+          <t>48093</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>86510</t>
+          <t>85399</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>90786</t>
+          <t>91922</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>141701</t>
+          <t>140650</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44341</t>
+          <t>44128</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>79341</t>
+          <t>81725</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37802</t>
+          <t>38753</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66515</t>
+          <t>68317</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>90839</t>
+          <t>89705</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>139322</t>
+          <t>136619</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>506701</t>
+          <t>506842</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>553061</t>
+          <t>552650</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>551011</t>
+          <t>546996</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>594601</t>
+          <t>593695</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1067485</t>
+          <t>1070421</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1132391</t>
+          <t>1134518</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,4%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29367</t>
+          <t>27406</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60415</t>
+          <t>59229</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16044</t>
+          <t>16118</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40018</t>
+          <t>39910</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>47047</t>
+          <t>48691</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>87307</t>
+          <t>90647</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24224</t>
+          <t>24318</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>53241</t>
+          <t>56061</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>33807</t>
+          <t>33513</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>60943</t>
+          <t>61881</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>63310</t>
+          <t>62485</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>104776</t>
+          <t>104157</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>419479</t>
+          <t>417367</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>458023</t>
+          <t>459960</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>425343</t>
+          <t>424858</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>459419</t>
+          <t>460047</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>857428</t>
+          <t>856375</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>909727</t>
+          <t>912575</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>88,19%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6480</t>
+          <t>6525</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26322</t>
+          <t>25213</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7850</t>
+          <t>7879</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>26705</t>
+          <t>28089</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>18838</t>
+          <t>18334</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>44479</t>
+          <t>44291</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17314</t>
+          <t>17933</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>43102</t>
+          <t>43080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>24137</t>
+          <t>24518</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>48543</t>
+          <t>50316</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,47 +2720,47 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
+          <t>6,07%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>12,45%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>63768</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>47185</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>82228</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>8,06%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
           <t>5,97%</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>12,02%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>63768</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>47166</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>81843</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>8,06%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>5,97%</t>
-        </is>
-      </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,4%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>327729</t>
+          <t>325810</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>357274</t>
+          <t>355415</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>337254</t>
+          <t>334756</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>366506</t>
+          <t>366488</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>673376</t>
+          <t>673899</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>715227</t>
+          <t>716752</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,65%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4494</t>
+          <t>3208</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>18991</t>
+          <t>18637</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9291</t>
+          <t>11591</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4988</t>
+          <t>4831</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>23139</t>
+          <t>23063</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12186</t>
+          <t>12854</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>35090</t>
+          <t>35996</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>18014</t>
+          <t>17723</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>38881</t>
+          <t>38576</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>35295</t>
+          <t>36113</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>65625</t>
+          <t>66171</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>245457</t>
+          <t>245463</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>271826</t>
+          <t>271825</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>300041</t>
+          <t>299113</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>322756</t>
+          <t>322324</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>555195</t>
+          <t>554307</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>589373</t>
+          <t>588970</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,68%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1577</t>
+          <t>1543</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>15488</t>
+          <t>15134</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>13351</t>
+          <t>12790</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3637</t>
+          <t>4534</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>19723</t>
+          <t>21280</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8339</t>
+          <t>8182</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>28706</t>
+          <t>27326</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>7043</t>
+          <t>7021</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>24355</t>
+          <t>23811</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>19847</t>
+          <t>18357</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>46658</t>
+          <t>44911</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>174181</t>
+          <t>173854</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>196614</t>
+          <t>196890</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>303773</t>
+          <t>304063</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>324077</t>
+          <t>323951</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>486691</t>
+          <t>485843</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>516894</t>
+          <t>515890</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,87%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>175089</t>
+          <t>174306</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>239375</t>
+          <t>239426</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>188925</t>
+          <t>192710</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>260829</t>
+          <t>260917</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>385425</t>
+          <t>381417</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>482913</t>
+          <t>484671</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>233863</t>
+          <t>235995</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>314410</t>
+          <t>316319</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>219556</t>
+          <t>220515</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>280947</t>
+          <t>282692</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>470374</t>
+          <t>476262</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>575599</t>
+          <t>580058</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2746504</t>
+          <t>2749724</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2845669</t>
+          <t>2847351</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2853356</t>
+          <t>2858073</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2950493</t>
+          <t>2946200</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>5635560</t>
+          <t>5630879</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5771939</t>
+          <t>5772031</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4421,7 +4421,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su lugar de nacimiento en 2012</t>
+          <t>Población según su lugar de nacimiento en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4616,12 +4616,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21698</t>
+          <t>20792</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45089</t>
+          <t>43903</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20655</t>
+          <t>20122</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42225</t>
+          <t>42675</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4666,12 +4666,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47628</t>
+          <t>45716</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>80637</t>
+          <t>79028</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4701,12 +4701,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,94%</t>
         </is>
       </c>
     </row>
@@ -4729,12 +4729,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16762</t>
+          <t>16745</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46643</t>
+          <t>45369</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12527</t>
+          <t>12637</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39005</t>
+          <t>38422</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4779,12 +4779,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35935</t>
+          <t>35730</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>73271</t>
+          <t>75047</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4814,12 +4814,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -4842,12 +4842,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>373371</t>
+          <t>374715</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>409849</t>
+          <t>408993</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>360388</t>
+          <t>360426</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>390911</t>
+          <t>392093</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>743960</t>
+          <t>745307</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>790510</t>
+          <t>793173</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,69%</t>
         </is>
       </c>
     </row>
@@ -5072,12 +5072,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>45113</t>
+          <t>46065</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>76220</t>
+          <t>78911</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>57062</t>
+          <t>57975</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>91037</t>
+          <t>92018</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>111772</t>
+          <t>109544</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>159065</t>
+          <t>158300</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,2%</t>
         </is>
       </c>
     </row>
@@ -5185,12 +5185,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>54658</t>
+          <t>54313</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>97709</t>
+          <t>98746</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>54189</t>
+          <t>53271</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>93320</t>
+          <t>95537</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>117273</t>
+          <t>118541</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>176681</t>
+          <t>180817</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,94%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>527983</t>
+          <t>526541</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>576120</t>
+          <t>577168</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>440002</t>
+          <t>437843</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>487286</t>
+          <t>487525</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>981246</t>
+          <t>980226</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1053410</t>
+          <t>1050991</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>81,01%</t>
         </is>
       </c>
     </row>
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>42539</t>
+          <t>43551</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>74699</t>
+          <t>74841</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>54322</t>
+          <t>54486</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>88308</t>
+          <t>87898</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>104637</t>
+          <t>107726</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>151331</t>
+          <t>152054</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,92%</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>65100</t>
+          <t>65304</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>113641</t>
+          <t>112092</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>64796</t>
+          <t>65366</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>112251</t>
+          <t>110539</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>140431</t>
+          <t>139374</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>205772</t>
+          <t>206392</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,82%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>509915</t>
+          <t>509325</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>562049</t>
+          <t>562691</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>524353</t>
+          <t>526575</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>579396</t>
+          <t>578980</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>74,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1054887</t>
+          <t>1057201</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1130302</t>
+          <t>1128261</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>81,01%</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26381</t>
+          <t>25365</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54077</t>
+          <t>53706</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20490</t>
+          <t>20336</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44458</t>
+          <t>43567</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6034,47 +6034,47 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
+          <t>7,07%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>68854</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>52433</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>88685</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>5,59%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>4,26%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
           <t>7,21%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>68854</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>52909</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>88025</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>5,59%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>4,3%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>46676</t>
+          <t>45289</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>89536</t>
+          <t>87760</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>59569</t>
+          <t>58534</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>106587</t>
+          <t>102869</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>116819</t>
+          <t>116134</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>174794</t>
+          <t>177704</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,44%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>483814</t>
+          <t>484765</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>532598</t>
+          <t>531241</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>479466</t>
+          <t>481911</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>528334</t>
+          <t>529671</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>977471</t>
+          <t>978723</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1050954</t>
+          <t>1048309</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,17%</t>
         </is>
       </c>
     </row>
@@ -6440,12 +6440,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5822</t>
+          <t>5566</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22240</t>
+          <t>23434</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>6135</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>21290</t>
+          <t>21390</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>15885</t>
+          <t>15639</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>38388</t>
+          <t>39066</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -6553,12 +6553,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19970</t>
+          <t>19902</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>49811</t>
+          <t>51319</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>33403</t>
+          <t>32812</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>67777</t>
+          <t>67843</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>60988</t>
+          <t>60263</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>109072</t>
+          <t>105371</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,01%</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>367334</t>
+          <t>365615</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>399062</t>
+          <t>398732</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>367387</t>
+          <t>366901</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>403786</t>
+          <t>404078</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>742975</t>
+          <t>744170</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>795504</t>
+          <t>793968</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,51%</t>
         </is>
       </c>
     </row>
@@ -6896,12 +6896,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1361</t>
+          <t>1348</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9935</t>
+          <t>11111</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6916,7 +6916,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2406</t>
+          <t>2434</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13702</t>
+          <t>14074</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5071</t>
+          <t>5595</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>19779</t>
+          <t>21631</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -7009,12 +7009,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>30304</t>
+          <t>30389</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>62826</t>
+          <t>64637</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>19754</t>
+          <t>21176</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>46851</t>
+          <t>47346</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>55354</t>
+          <t>57020</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>100811</t>
+          <t>102267</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,41%</t>
         </is>
       </c>
     </row>
@@ -7122,12 +7122,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>242862</t>
+          <t>241251</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>275755</t>
+          <t>275743</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -7157,12 +7157,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>299449</t>
+          <t>299142</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>327494</t>
+          <t>327837</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>551952</t>
+          <t>550688</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>596821</t>
+          <t>596105</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,8%</t>
         </is>
       </c>
     </row>
@@ -7352,12 +7352,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>11051</t>
+          <t>11019</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3929</t>
+          <t>3887</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>17225</t>
+          <t>18084</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6565</t>
+          <t>6772</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>22351</t>
+          <t>24001</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>13716</t>
+          <t>15711</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>42372</t>
+          <t>42446</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4034</t>
+          <t>5860</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>24875</t>
+          <t>25293</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>23694</t>
+          <t>25060</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>60508</t>
+          <t>58519</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -7578,12 +7578,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>202249</t>
+          <t>203935</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>232068</t>
+          <t>230507</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>354305</t>
+          <t>354477</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>376576</t>
+          <t>377107</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>567142</t>
+          <t>566292</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>603026</t>
+          <t>601418</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7663,12 +7663,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,14%</t>
         </is>
       </c>
     </row>
@@ -7808,12 +7808,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>179591</t>
+          <t>180123</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>239642</t>
+          <t>242768</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>199087</t>
+          <t>202050</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>264604</t>
+          <t>261790</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>393752</t>
+          <t>400250</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>485907</t>
+          <t>484349</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7893,12 +7893,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>312621</t>
+          <t>314381</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>412346</t>
+          <t>416613</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>306152</t>
+          <t>308447</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>408217</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>641348</t>
+          <t>645546</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>777150</t>
+          <t>786431</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8006,12 +8006,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,26%</t>
         </is>
       </c>
     </row>
@@ -8034,12 +8034,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2806691</t>
+          <t>2795138</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2912479</t>
+          <t>2910291</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2920951</t>
+          <t>2918346</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3030426</t>
+          <t>3027045</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>5759187</t>
+          <t>5751375</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5913484</t>
+          <t>5904723</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8119,12 +8119,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>84,53%</t>
         </is>
       </c>
     </row>
@@ -8304,7 +8304,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su lugar de nacimiento en 2016</t>
+          <t>Población según su lugar de nacimiento en 2016 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8499,12 +8499,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28428</t>
+          <t>29194</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>57547</t>
+          <t>58819</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8514,12 +8514,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15870</t>
+          <t>15817</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35940</t>
+          <t>35877</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8549,12 +8549,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50410</t>
+          <t>50569</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>83514</t>
+          <t>84113</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8584,12 +8584,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,32%</t>
         </is>
       </c>
     </row>
@@ -8612,12 +8612,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15309</t>
+          <t>15324</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40027</t>
+          <t>41674</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8632,7 +8632,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8647,12 +8647,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12383</t>
+          <t>12726</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34123</t>
+          <t>34139</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8662,12 +8662,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8682,12 +8682,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32391</t>
+          <t>34664</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>66540</t>
+          <t>66574</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8697,12 +8697,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>330921</t>
+          <t>331799</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>368505</t>
+          <t>369155</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>333489</t>
+          <t>333444</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>362010</t>
+          <t>362413</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>676837</t>
+          <t>676538</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>722393</t>
+          <t>721357</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,49%</t>
         </is>
       </c>
     </row>
@@ -8955,12 +8955,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>41949</t>
+          <t>41971</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>74231</t>
+          <t>74006</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>40685</t>
+          <t>39674</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>68601</t>
+          <t>67908</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9025,12 +9025,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>91512</t>
+          <t>90335</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>133568</t>
+          <t>132406</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9040,12 +9040,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,47%</t>
         </is>
       </c>
     </row>
@@ -9068,12 +9068,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32044</t>
+          <t>32091</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>65687</t>
+          <t>64812</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9103,12 +9103,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29424</t>
+          <t>28010</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>57979</t>
+          <t>57607</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9118,12 +9118,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9138,12 +9138,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>67461</t>
+          <t>67503</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>112053</t>
+          <t>111707</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9158,7 +9158,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,68%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>464293</t>
+          <t>464513</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>508032</t>
+          <t>509035</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>449282</t>
+          <t>449019</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>486138</t>
+          <t>486636</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>923560</t>
+          <t>927014</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>983744</t>
+          <t>984396</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,3%</t>
         </is>
       </c>
     </row>
@@ -9411,12 +9411,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>39608</t>
+          <t>38716</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>72110</t>
+          <t>69598</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>56345</t>
+          <t>55982</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>87812</t>
+          <t>88931</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9481,12 +9481,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>101274</t>
+          <t>104780</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>148880</t>
+          <t>150402</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9496,12 +9496,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,3%</t>
         </is>
       </c>
     </row>
@@ -9524,12 +9524,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>60501</t>
+          <t>59929</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>99952</t>
+          <t>101618</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>66043</t>
+          <t>64447</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>108270</t>
+          <t>104963</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9594,12 +9594,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>136516</t>
+          <t>135746</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>194856</t>
+          <t>193188</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9609,12 +9609,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,52%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>509442</t>
+          <t>510722</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>558329</t>
+          <t>557961</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>482484</t>
+          <t>481823</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>529612</t>
+          <t>528203</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>72,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1009032</t>
+          <t>1007906</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1077626</t>
+          <t>1073578</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>75,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>80,69%</t>
         </is>
       </c>
     </row>
@@ -9867,12 +9867,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28661</t>
+          <t>28238</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>57087</t>
+          <t>57174</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35052</t>
+          <t>35995</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>63829</t>
+          <t>63460</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>71299</t>
+          <t>70598</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>112058</t>
+          <t>110215</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9952,12 +9952,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -9980,12 +9980,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>55311</t>
+          <t>55519</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>96888</t>
+          <t>95654</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>40609</t>
+          <t>40842</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>77216</t>
+          <t>77482</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10050,12 +10050,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>108565</t>
+          <t>104892</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>160451</t>
+          <t>159790</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10065,12 +10065,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,34%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>505248</t>
+          <t>505617</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>553693</t>
+          <t>553049</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>78,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>519277</t>
+          <t>520898</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>563948</t>
+          <t>561920</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1041560</t>
+          <t>1042940</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1103350</t>
+          <t>1105277</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,34%</t>
         </is>
       </c>
     </row>
@@ -10323,12 +10323,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4358</t>
+          <t>4257</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20114</t>
+          <t>20359</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>14798</t>
+          <t>15264</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>35055</t>
+          <t>35141</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10393,12 +10393,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>23032</t>
+          <t>22683</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>47417</t>
+          <t>48313</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10408,12 +10408,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -10436,12 +10436,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>23520</t>
+          <t>23877</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>53929</t>
+          <t>55738</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>25962</t>
+          <t>26150</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>58522</t>
+          <t>57877</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10506,12 +10506,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>57233</t>
+          <t>53267</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>102166</t>
+          <t>99960</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10521,12 +10521,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,25%</t>
         </is>
       </c>
     </row>
@@ -10549,12 +10549,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>414234</t>
+          <t>410532</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>447049</t>
+          <t>444835</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>412637</t>
+          <t>415502</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>450983</t>
+          <t>450550</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10619,12 +10619,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>836507</t>
+          <t>839339</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>886682</t>
+          <t>890185</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10634,12 +10634,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>91,32%</t>
         </is>
       </c>
     </row>
@@ -10784,7 +10784,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8189</t>
+          <t>10324</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>3493</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>15525</t>
+          <t>16374</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10849,12 +10849,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4950</t>
+          <t>4970</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>19520</t>
+          <t>20022</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10869,7 +10869,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -10892,12 +10892,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>24746</t>
+          <t>24958</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>52452</t>
+          <t>53051</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>22390</t>
+          <t>22613</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>49834</t>
+          <t>50640</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10962,12 +10962,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>53125</t>
+          <t>54457</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>96318</t>
+          <t>94153</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10977,12 +10977,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,22%</t>
         </is>
       </c>
     </row>
@@ -11005,12 +11005,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>277965</t>
+          <t>278481</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>306843</t>
+          <t>307241</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>319195</t>
+          <t>316998</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>348456</t>
+          <t>347947</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11075,12 +11075,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>605778</t>
+          <t>606609</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>649074</t>
+          <t>648729</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11090,12 +11090,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,1%</t>
         </is>
       </c>
     </row>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6396</t>
+          <t>7383</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8786</t>
+          <t>10154</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11290,7 +11290,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11305,12 +11305,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>1386</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>12735</t>
+          <t>11843</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11320,12 +11320,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -11348,12 +11348,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9577</t>
+          <t>9773</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>27285</t>
+          <t>26474</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>30406</t>
+          <t>30188</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>66255</t>
+          <t>64885</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -11418,12 +11418,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>45315</t>
+          <t>44068</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>86098</t>
+          <t>86399</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -11433,12 +11433,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,15%</t>
         </is>
       </c>
     </row>
@@ -11461,12 +11461,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>227337</t>
+          <t>227915</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>245515</t>
+          <t>245890</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>331096</t>
+          <t>332254</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>367471</t>
+          <t>367058</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11531,12 +11531,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>563933</t>
+          <t>566499</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>607317</t>
+          <t>608393</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11546,12 +11546,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,58%</t>
         </is>
       </c>
     </row>
@@ -11691,12 +11691,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>178099</t>
+          <t>178617</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>239796</t>
+          <t>241047</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>203574</t>
+          <t>202153</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>262822</t>
+          <t>259728</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11761,12 +11761,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>397100</t>
+          <t>400298</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>486008</t>
+          <t>482043</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11776,12 +11776,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -11804,12 +11804,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>275046</t>
+          <t>274204</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>357798</t>
+          <t>357739</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11819,7 +11819,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>284066</t>
+          <t>282727</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>371657</t>
+          <t>372028</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -11874,12 +11874,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>588141</t>
+          <t>581689</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>707018</t>
+          <t>702024</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -11889,12 +11889,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -11917,12 +11917,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2821058</t>
+          <t>2821365</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2917402</t>
+          <t>2919471</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2934849</t>
+          <t>2934563</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3036508</t>
+          <t>3040168</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -11987,12 +11987,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>5784760</t>
+          <t>5789390</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5924398</t>
+          <t>5930353</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12002,12 +12002,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,47%</t>
         </is>
       </c>
     </row>
@@ -12187,7 +12187,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su lugar de nacimiento en 2023</t>
+          <t>Población según su lugar de nacimiento en 2023 (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1908</t>
+          <t>1862</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4874</t>
+          <t>5091</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -12397,12 +12397,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -12417,12 +12417,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>1823</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4670</t>
+          <t>4577</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4429</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8726</t>
+          <t>8548</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -12495,12 +12495,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4207</t>
+          <t>4119</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36811</t>
+          <t>37533</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -12510,12 +12510,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -12530,12 +12530,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3021</t>
+          <t>3155</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19043</t>
+          <t>19550</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9476</t>
+          <t>10899</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44515</t>
+          <t>46684</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,55%</t>
         </is>
       </c>
     </row>
@@ -12608,12 +12608,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>359395</t>
+          <t>359364</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>392627</t>
+          <t>392789</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -12623,12 +12623,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -12643,12 +12643,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>290988</t>
+          <t>291036</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>307461</t>
+          <t>307666</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -12658,12 +12658,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -12678,12 +12678,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>661573</t>
+          <t>660347</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>697047</t>
+          <t>695951</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -12693,12 +12693,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,58%</t>
         </is>
       </c>
     </row>
@@ -12838,12 +12838,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3629</t>
+          <t>3552</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7372</t>
+          <t>7418</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12853,47 +12853,47 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>10102</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>7663</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>12955</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
           <t>1,74%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>10102</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>7615</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>13171</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>2,29%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12469</t>
+          <t>12237</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>18893</t>
+          <t>18839</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -12951,12 +12951,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11702</t>
+          <t>12038</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>37512</t>
+          <t>37813</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -12966,12 +12966,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -12986,12 +12986,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14359</t>
+          <t>13991</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34614</t>
+          <t>33833</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -13001,12 +13001,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -13021,12 +13021,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>30382</t>
+          <t>31168</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>62752</t>
+          <t>64018</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -13036,12 +13036,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,4%</t>
         </is>
       </c>
     </row>
@@ -13064,12 +13064,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>381034</t>
+          <t>380763</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>406788</t>
+          <t>406251</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -13079,12 +13079,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -13099,12 +13099,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>396116</t>
+          <t>397612</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>417046</t>
+          <t>417799</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -13114,12 +13114,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -13134,12 +13134,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>785937</t>
+          <t>784784</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>819454</t>
+          <t>818553</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -13149,12 +13149,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,68%</t>
         </is>
       </c>
     </row>
@@ -13294,12 +13294,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9002</t>
+          <t>8974</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14809</t>
+          <t>14510</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -13309,12 +13309,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -13329,12 +13329,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13765</t>
+          <t>13556</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20235</t>
+          <t>20487</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -13344,12 +13344,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -13364,12 +13364,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>24188</t>
+          <t>24455</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>32704</t>
+          <t>32997</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -13379,12 +13379,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -13407,12 +13407,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16299</t>
+          <t>16979</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37527</t>
+          <t>36641</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -13422,12 +13422,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -13442,12 +13442,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23321</t>
+          <t>23486</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40759</t>
+          <t>42310</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -13457,12 +13457,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -13477,12 +13477,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44753</t>
+          <t>44149</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>73281</t>
+          <t>71319</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -13492,12 +13492,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -13520,12 +13520,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>486534</t>
+          <t>487303</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>508935</t>
+          <t>507765</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -13535,12 +13535,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -13555,12 +13555,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>484390</t>
+          <t>484065</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>503103</t>
+          <t>503653</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -13570,12 +13570,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -13590,12 +13590,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>976899</t>
+          <t>978728</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1005766</t>
+          <t>1006956</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -13605,12 +13605,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,34%</t>
         </is>
       </c>
     </row>
@@ -13750,12 +13750,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>5964</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10950</t>
+          <t>11102</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13785,12 +13785,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11296</t>
+          <t>11554</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17462</t>
+          <t>17862</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13800,12 +13800,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13820,12 +13820,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18731</t>
+          <t>18837</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26436</t>
+          <t>26500</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13863,12 +13863,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32006</t>
+          <t>32474</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>57862</t>
+          <t>58876</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13878,12 +13878,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13898,12 +13898,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26522</t>
+          <t>26925</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>44239</t>
+          <t>45681</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13913,12 +13913,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13933,12 +13933,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>64723</t>
+          <t>65510</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>96517</t>
+          <t>95237</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13948,12 +13948,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -13976,12 +13976,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>567641</t>
+          <t>566933</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>594272</t>
+          <t>593948</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13991,12 +13991,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -14011,12 +14011,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>610979</t>
+          <t>610077</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>629513</t>
+          <t>629422</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -14026,12 +14026,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -14046,12 +14046,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1185345</t>
+          <t>1186102</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1217496</t>
+          <t>1217015</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -14061,12 +14061,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,32%</t>
         </is>
       </c>
     </row>
@@ -14206,12 +14206,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>5386</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9717</t>
+          <t>9806</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -14226,7 +14226,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -14241,12 +14241,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7056</t>
+          <t>7242</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12219</t>
+          <t>12023</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -14256,12 +14256,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -14276,12 +14276,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>13658</t>
+          <t>13896</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20148</t>
+          <t>20330</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -14291,12 +14291,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -14319,12 +14319,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>22735</t>
+          <t>23272</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>43676</t>
+          <t>44841</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -14334,12 +14334,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -14354,12 +14354,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>19001</t>
+          <t>18694</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>33829</t>
+          <t>34111</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -14369,12 +14369,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -14389,12 +14389,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>44975</t>
+          <t>46099</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>71631</t>
+          <t>71717</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -14404,12 +14404,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -14432,12 +14432,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>509279</t>
+          <t>508838</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>531893</t>
+          <t>530091</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -14447,12 +14447,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -14467,12 +14467,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>501875</t>
+          <t>501307</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>517828</t>
+          <t>517873</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -14482,12 +14482,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -14502,12 +14502,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1017024</t>
+          <t>1017394</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1044858</t>
+          <t>1043654</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -14517,12 +14517,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,33%</t>
         </is>
       </c>
     </row>
@@ -14662,12 +14662,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>1929</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4981</t>
+          <t>4907</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -14677,12 +14677,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -14697,12 +14697,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2878</t>
+          <t>2812</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6203</t>
+          <t>6020</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -14712,12 +14712,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14732,12 +14732,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5641</t>
+          <t>5573</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10054</t>
+          <t>9835</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14752,7 +14752,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -14775,12 +14775,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>16988</t>
+          <t>16768</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>33328</t>
+          <t>33063</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14790,12 +14790,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14810,12 +14810,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>20009</t>
+          <t>20093</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>34324</t>
+          <t>34873</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14825,12 +14825,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14845,12 +14845,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>40052</t>
+          <t>40336</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>61278</t>
+          <t>61281</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14860,7 +14860,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -14888,12 +14888,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>331706</t>
+          <t>331747</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>348210</t>
+          <t>348169</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14903,12 +14903,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14923,12 +14923,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>361394</t>
+          <t>360835</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>376013</t>
+          <t>376175</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14938,12 +14938,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14958,12 +14958,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>699298</t>
+          <t>698352</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>720702</t>
+          <t>720365</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14973,12 +14973,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,78%</t>
         </is>
       </c>
     </row>
@@ -15118,12 +15118,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>961</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3010</t>
+          <t>3167</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -15153,12 +15153,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1432</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4112</t>
+          <t>3863</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -15173,7 +15173,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -15188,12 +15188,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2740</t>
+          <t>2760</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6036</t>
+          <t>6021</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -15231,12 +15231,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9790</t>
+          <t>9907</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>22496</t>
+          <t>22307</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -15246,12 +15246,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -15266,12 +15266,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>14704</t>
+          <t>14563</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>27106</t>
+          <t>27314</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -15281,12 +15281,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -15301,12 +15301,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>27797</t>
+          <t>27174</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>47001</t>
+          <t>45488</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -15316,12 +15316,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,43%</t>
         </is>
       </c>
     </row>
@@ -15344,12 +15344,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>258398</t>
+          <t>258737</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>271291</t>
+          <t>271125</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -15359,12 +15359,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -15379,12 +15379,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>395095</t>
+          <t>395094</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>407779</t>
+          <t>407857</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -15399,7 +15399,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -15414,12 +15414,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>656672</t>
+          <t>657770</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>676052</t>
+          <t>676529</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -15429,12 +15429,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,6%</t>
         </is>
       </c>
     </row>
@@ -15574,12 +15574,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>36091</t>
+          <t>35406</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>46288</t>
+          <t>45613</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -15589,12 +15589,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -15609,12 +15609,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>53900</t>
+          <t>53601</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>66827</t>
+          <t>66061</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -15624,12 +15624,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -15644,12 +15644,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>92172</t>
+          <t>92570</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>107747</t>
+          <t>108929</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -15664,7 +15664,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -15687,12 +15687,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>151201</t>
+          <t>151383</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>212061</t>
+          <t>211277</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -15707,7 +15707,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -15722,12 +15722,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>150494</t>
+          <t>150137</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>192042</t>
+          <t>192495</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -15737,12 +15737,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -15757,12 +15757,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>311933</t>
+          <t>315783</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>387820</t>
+          <t>391168</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -15772,12 +15772,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -15800,12 +15800,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2954531</t>
+          <t>2954503</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3015303</t>
+          <t>3013607</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -15820,7 +15820,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -15835,12 +15835,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>3083494</t>
+          <t>3082487</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3127588</t>
+          <t>3128547</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -15850,12 +15850,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -15870,12 +15870,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>6055076</t>
+          <t>6048659</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6132702</t>
+          <t>6126963</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -15885,12 +15885,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,64%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P58-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P58-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25120</t>
+          <t>24427</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51981</t>
+          <t>52147</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28721</t>
+          <t>28725</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57864</t>
+          <t>58645</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60034</t>
+          <t>60471</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>102057</t>
+          <t>101698</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,58%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17056</t>
+          <t>16968</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42863</t>
+          <t>43472</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14351</t>
+          <t>14460</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32828</t>
+          <t>34132</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>37126</t>
+          <t>37438</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>67922</t>
+          <t>68536</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>409799</t>
+          <t>408115</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>444398</t>
+          <t>444148</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>385406</t>
+          <t>384012</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>418509</t>
+          <t>418285</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>806057</t>
+          <t>807164</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>857963</t>
+          <t>854230</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>88,84%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>32757</t>
+          <t>34606</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>65013</t>
+          <t>67113</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>52844</t>
+          <t>50732</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>90424</t>
+          <t>90251</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>95779</t>
+          <t>92576</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>142969</t>
+          <t>143435</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,54%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>59386</t>
+          <t>59822</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>103879</t>
+          <t>100489</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>41123</t>
+          <t>41598</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>71045</t>
+          <t>71705</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>109466</t>
+          <t>109720</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>163923</t>
+          <t>161563</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,87%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>581060</t>
+          <t>580008</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>630776</t>
+          <t>630044</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,0%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>478526</t>
+          <t>476391</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>523406</t>
+          <t>523782</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1074695</t>
+          <t>1072501</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1142042</t>
+          <t>1138755</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>83,67%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>32990</t>
+          <t>32442</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>64874</t>
+          <t>65503</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>48093</t>
+          <t>49204</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>85399</t>
+          <t>87409</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>91922</t>
+          <t>90911</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>140650</t>
+          <t>140538</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,58%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44128</t>
+          <t>43218</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>81725</t>
+          <t>80057</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38753</t>
+          <t>36771</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68317</t>
+          <t>66466</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>89705</t>
+          <t>88350</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>136619</t>
+          <t>137863</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>506842</t>
+          <t>505935</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>552650</t>
+          <t>552050</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>546996</t>
+          <t>546442</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>593695</t>
+          <t>594149</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1070421</t>
+          <t>1069134</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1134518</t>
+          <t>1134786</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,42%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27406</t>
+          <t>28135</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>59229</t>
+          <t>61314</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16118</t>
+          <t>15908</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39910</t>
+          <t>41674</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>48691</t>
+          <t>50559</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>90647</t>
+          <t>90351</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,73%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24318</t>
+          <t>22807</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>56061</t>
+          <t>53812</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>33513</t>
+          <t>33647</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>61881</t>
+          <t>59843</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>62485</t>
+          <t>64629</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>104157</t>
+          <t>103813</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,03%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>417367</t>
+          <t>417210</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>459960</t>
+          <t>458767</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>424858</t>
+          <t>422684</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>460047</t>
+          <t>459678</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>856375</t>
+          <t>858753</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>912575</t>
+          <t>910543</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>87,99%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6525</t>
+          <t>7607</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>25213</t>
+          <t>25132</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7879</t>
+          <t>7820</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>28089</t>
+          <t>27609</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>18334</t>
+          <t>18822</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>44291</t>
+          <t>44721</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17933</t>
+          <t>18323</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>43080</t>
+          <t>42735</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>24518</t>
+          <t>24579</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>50316</t>
+          <t>48648</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>47185</t>
+          <t>47556</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>82228</t>
+          <t>83818</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,6%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>325810</t>
+          <t>328364</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>355415</t>
+          <t>356857</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>334756</t>
+          <t>336021</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>366488</t>
+          <t>366272</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>673899</t>
+          <t>673594</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>716752</t>
+          <t>718804</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,91%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>3177</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>18637</t>
+          <t>18566</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11591</t>
+          <t>8737</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4831</t>
+          <t>6099</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>23063</t>
+          <t>24235</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12854</t>
+          <t>12962</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>35996</t>
+          <t>35091</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>17723</t>
+          <t>17629</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>38576</t>
+          <t>37959</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>36113</t>
+          <t>35347</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>66171</t>
+          <t>67316</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>245463</t>
+          <t>246181</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>271825</t>
+          <t>271737</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>299113</t>
+          <t>301283</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>322324</t>
+          <t>322732</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>554307</t>
+          <t>554623</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>588970</t>
+          <t>589487</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,76%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1543</t>
+          <t>1556</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>15134</t>
+          <t>14073</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>12790</t>
+          <t>14135</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4534</t>
+          <t>3472</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>21280</t>
+          <t>20008</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8182</t>
+          <t>8228</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>27326</t>
+          <t>28967</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>7021</t>
+          <t>6980</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>23811</t>
+          <t>23677</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>18357</t>
+          <t>19869</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>44911</t>
+          <t>46969</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>173854</t>
+          <t>175353</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>196890</t>
+          <t>196790</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>304063</t>
+          <t>304406</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>323951</t>
+          <t>324275</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>485843</t>
+          <t>485098</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>515890</t>
+          <t>516415</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,97%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>174306</t>
+          <t>172478</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>239426</t>
+          <t>242923</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>192710</t>
+          <t>192321</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>260917</t>
+          <t>264557</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>381417</t>
+          <t>381036</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>484671</t>
+          <t>478948</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>235995</t>
+          <t>235468</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>316319</t>
+          <t>318025</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>220515</t>
+          <t>217477</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>282692</t>
+          <t>280146</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>476262</t>
+          <t>471995</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>580058</t>
+          <t>578127</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2749724</t>
+          <t>2745881</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2847351</t>
+          <t>2848050</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2858073</t>
+          <t>2857046</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2946200</t>
+          <t>2948671</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>5630879</t>
+          <t>5640007</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5772031</t>
+          <t>5775166</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,77%</t>
         </is>
       </c>
     </row>
@@ -4616,12 +4616,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20792</t>
+          <t>20753</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43903</t>
+          <t>45074</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20122</t>
+          <t>19773</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42675</t>
+          <t>41541</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4666,12 +4666,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45716</t>
+          <t>45664</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>79028</t>
+          <t>79830</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4701,12 +4701,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,03%</t>
         </is>
       </c>
     </row>
@@ -4729,12 +4729,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16745</t>
+          <t>16890</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45369</t>
+          <t>46024</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4744,12 +4744,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12637</t>
+          <t>12321</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38422</t>
+          <t>38126</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4779,12 +4779,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35730</t>
+          <t>36559</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>75047</t>
+          <t>76419</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4814,12 +4814,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -4842,12 +4842,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>374715</t>
+          <t>373226</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>408993</t>
+          <t>408047</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>360426</t>
+          <t>358851</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>392093</t>
+          <t>391122</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>745307</t>
+          <t>746318</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>793173</t>
+          <t>792538</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,62%</t>
         </is>
       </c>
     </row>
@@ -5072,12 +5072,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>46065</t>
+          <t>46315</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>78911</t>
+          <t>78047</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>57975</t>
+          <t>57724</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>92018</t>
+          <t>89804</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>109544</t>
+          <t>112524</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>158300</t>
+          <t>159373</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,28%</t>
         </is>
       </c>
     </row>
@@ -5185,12 +5185,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>54313</t>
+          <t>54282</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>98746</t>
+          <t>97884</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5205,7 +5205,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>53271</t>
+          <t>54278</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>95537</t>
+          <t>96364</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>118541</t>
+          <t>119117</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>180817</t>
+          <t>178746</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,78%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>526541</t>
+          <t>527226</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>577168</t>
+          <t>576021</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>437843</t>
+          <t>440429</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>487525</t>
+          <t>487550</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>980226</t>
+          <t>980627</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1050991</t>
+          <t>1049080</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>80,86%</t>
         </is>
       </c>
     </row>
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>43551</t>
+          <t>42262</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>74841</t>
+          <t>74558</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>54486</t>
+          <t>54970</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>87898</t>
+          <t>89947</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>107726</t>
+          <t>105814</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>152054</t>
+          <t>153054</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,99%</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>65304</t>
+          <t>64410</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>112092</t>
+          <t>111175</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>65366</t>
+          <t>64126</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>110539</t>
+          <t>110360</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>139374</t>
+          <t>142814</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>206392</t>
+          <t>206270</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,81%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>509325</t>
+          <t>514266</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>562691</t>
+          <t>564261</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>526575</t>
+          <t>527097</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>578980</t>
+          <t>581218</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1057201</t>
+          <t>1053459</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1128261</t>
+          <t>1129010</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>81,07%</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25365</t>
+          <t>25977</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>53706</t>
+          <t>53619</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20336</t>
+          <t>21570</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>43567</t>
+          <t>44780</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>52433</t>
+          <t>53041</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>88685</t>
+          <t>89238</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>45289</t>
+          <t>45484</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>87760</t>
+          <t>88914</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>58534</t>
+          <t>58737</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>102869</t>
+          <t>101298</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>116134</t>
+          <t>114707</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>177704</t>
+          <t>177707</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6182,7 +6182,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>484765</t>
+          <t>484854</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>531241</t>
+          <t>533140</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>481911</t>
+          <t>482213</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>529671</t>
+          <t>528449</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>78,26%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>978723</t>
+          <t>982938</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1048309</t>
+          <t>1049901</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,3%</t>
         </is>
       </c>
     </row>
@@ -6440,12 +6440,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5566</t>
+          <t>5707</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>23434</t>
+          <t>22665</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>6207</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>21390</t>
+          <t>22695</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>15639</t>
+          <t>15404</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>39066</t>
+          <t>37544</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -6553,12 +6553,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19902</t>
+          <t>18157</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>51319</t>
+          <t>49559</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>32812</t>
+          <t>33123</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>67843</t>
+          <t>67207</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>60263</t>
+          <t>58189</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>105371</t>
+          <t>104496</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,91%</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>365615</t>
+          <t>365429</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>398732</t>
+          <t>399903</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>366901</t>
+          <t>365967</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>404078</t>
+          <t>403972</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>744170</t>
+          <t>745108</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>793968</t>
+          <t>793877</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,5%</t>
         </is>
       </c>
     </row>
@@ -6896,12 +6896,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>771</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11111</t>
+          <t>11268</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2434</t>
+          <t>2369</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14074</t>
+          <t>13566</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5595</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>21631</t>
+          <t>21209</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -7009,12 +7009,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>30389</t>
+          <t>29381</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>64637</t>
+          <t>61757</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>21176</t>
+          <t>20055</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>47346</t>
+          <t>47157</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>57020</t>
+          <t>55217</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>102267</t>
+          <t>97567</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>14,7%</t>
         </is>
       </c>
     </row>
@@ -7122,12 +7122,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>241251</t>
+          <t>243030</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>275743</t>
+          <t>277627</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7157,12 +7157,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>299142</t>
+          <t>299222</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>327837</t>
+          <t>327213</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>550688</t>
+          <t>554324</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>596105</t>
+          <t>597740</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>90,05%</t>
         </is>
       </c>
     </row>
@@ -7352,12 +7352,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>11019</t>
+          <t>10274</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3887</t>
+          <t>3831</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>18084</t>
+          <t>16963</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6772</t>
+          <t>6507</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>24001</t>
+          <t>23105</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>15711</t>
+          <t>15473</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>42446</t>
+          <t>42145</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>5860</t>
+          <t>4024</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>25293</t>
+          <t>26938</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>25060</t>
+          <t>23130</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>58519</t>
+          <t>58993</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -7578,12 +7578,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>203935</t>
+          <t>204453</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>230507</t>
+          <t>231552</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>81,83%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>354477</t>
+          <t>353392</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>377107</t>
+          <t>377776</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>566292</t>
+          <t>565101</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>601418</t>
+          <t>603932</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7663,12 +7663,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,54%</t>
         </is>
       </c>
     </row>
@@ -7808,12 +7808,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>180123</t>
+          <t>180293</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>242768</t>
+          <t>238616</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7828,7 +7828,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>202050</t>
+          <t>203211</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>261790</t>
+          <t>268587</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>400250</t>
+          <t>398292</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>484349</t>
+          <t>486521</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7893,12 +7893,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>314381</t>
+          <t>309837</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>416613</t>
+          <t>411428</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>308447</t>
+          <t>307810</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>408217</t>
+          <t>401156</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>645546</t>
+          <t>643726</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>786431</t>
+          <t>777752</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8006,12 +8006,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,13%</t>
         </is>
       </c>
     </row>
@@ -8034,12 +8034,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2795138</t>
+          <t>2803532</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2910291</t>
+          <t>2911479</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2918346</t>
+          <t>2917725</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3027045</t>
+          <t>3027214</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>5751375</t>
+          <t>5759053</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5904723</t>
+          <t>5911883</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8119,12 +8119,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,64%</t>
         </is>
       </c>
     </row>
@@ -8499,12 +8499,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29194</t>
+          <t>29592</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58819</t>
+          <t>57587</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8514,12 +8514,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15817</t>
+          <t>16976</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35877</t>
+          <t>36595</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8549,12 +8549,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50569</t>
+          <t>51690</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84113</t>
+          <t>84981</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8584,12 +8584,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,42%</t>
         </is>
       </c>
     </row>
@@ -8612,12 +8612,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15324</t>
+          <t>15591</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>41674</t>
+          <t>39895</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8627,12 +8627,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8647,12 +8647,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12726</t>
+          <t>12824</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34139</t>
+          <t>35452</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8662,12 +8662,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8682,12 +8682,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34664</t>
+          <t>34697</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>66574</t>
+          <t>66826</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8697,12 +8697,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>331799</t>
+          <t>331514</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>369155</t>
+          <t>368819</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>333444</t>
+          <t>333741</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>362413</t>
+          <t>361710</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>676538</t>
+          <t>676464</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>721357</t>
+          <t>719921</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,31%</t>
         </is>
       </c>
     </row>
@@ -8955,12 +8955,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>41971</t>
+          <t>42641</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>74006</t>
+          <t>75037</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>39674</t>
+          <t>39177</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>67908</t>
+          <t>66225</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9025,12 +9025,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>90335</t>
+          <t>91028</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>132406</t>
+          <t>133889</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9040,12 +9040,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,6%</t>
         </is>
       </c>
     </row>
@@ -9068,12 +9068,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32091</t>
+          <t>33179</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>64812</t>
+          <t>64785</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9083,12 +9083,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9103,12 +9103,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28010</t>
+          <t>26357</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>57607</t>
+          <t>57337</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9118,12 +9118,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9138,12 +9138,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>67503</t>
+          <t>68314</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>111707</t>
+          <t>111449</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9153,12 +9153,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,66%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>464513</t>
+          <t>463486</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>509035</t>
+          <t>506422</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>78,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>449019</t>
+          <t>447717</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>486636</t>
+          <t>486901</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>927014</t>
+          <t>926669</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>984396</t>
+          <t>984514</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,31%</t>
         </is>
       </c>
     </row>
@@ -9411,12 +9411,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38716</t>
+          <t>37985</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>69598</t>
+          <t>68618</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>55982</t>
+          <t>56422</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>88931</t>
+          <t>88107</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9481,12 +9481,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>104780</t>
+          <t>104513</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>150402</t>
+          <t>145668</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9496,12 +9496,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>10,95%</t>
         </is>
       </c>
     </row>
@@ -9524,12 +9524,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>59929</t>
+          <t>61131</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>101618</t>
+          <t>102475</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>64447</t>
+          <t>66043</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>104963</t>
+          <t>105690</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9594,12 +9594,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>135746</t>
+          <t>133704</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>193188</t>
+          <t>195145</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9609,12 +9609,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,67%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>510722</t>
+          <t>511793</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>557961</t>
+          <t>558946</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>481823</t>
+          <t>483428</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>528203</t>
+          <t>528893</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1007906</t>
+          <t>1009692</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1073578</t>
+          <t>1075829</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,86%</t>
         </is>
       </c>
     </row>
@@ -9867,12 +9867,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28238</t>
+          <t>28178</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>57174</t>
+          <t>57440</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35995</t>
+          <t>35903</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>63460</t>
+          <t>64326</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>70598</t>
+          <t>72107</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>110215</t>
+          <t>112046</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9952,12 +9952,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,65%</t>
         </is>
       </c>
     </row>
@@ -9980,12 +9980,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>55519</t>
+          <t>53632</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>95654</t>
+          <t>94909</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>40842</t>
+          <t>41278</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>77482</t>
+          <t>77618</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10050,12 +10050,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>104892</t>
+          <t>106009</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>159790</t>
+          <t>161388</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10065,12 +10065,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,46%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>505617</t>
+          <t>509322</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>553049</t>
+          <t>554676</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>78,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>520898</t>
+          <t>519291</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>561920</t>
+          <t>564753</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1042940</t>
+          <t>1038498</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1105277</t>
+          <t>1104113</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,25%</t>
         </is>
       </c>
     </row>
@@ -10323,12 +10323,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4257</t>
+          <t>4304</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20359</t>
+          <t>19757</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15264</t>
+          <t>15035</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>35141</t>
+          <t>36093</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10393,12 +10393,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>22683</t>
+          <t>23103</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>48313</t>
+          <t>49040</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10408,12 +10408,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -10436,12 +10436,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>23877</t>
+          <t>24097</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>55738</t>
+          <t>55451</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>26150</t>
+          <t>25511</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>57877</t>
+          <t>58903</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10506,12 +10506,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>53267</t>
+          <t>56232</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>99960</t>
+          <t>99478</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10521,12 +10521,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -10549,12 +10549,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>410532</t>
+          <t>411424</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>444835</t>
+          <t>446012</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>415502</t>
+          <t>412716</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>450550</t>
+          <t>451124</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10619,12 +10619,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>839339</t>
+          <t>839419</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>890185</t>
+          <t>887576</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10639,7 +10639,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,06%</t>
         </is>
       </c>
     </row>
@@ -10784,7 +10784,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10324</t>
+          <t>9121</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3493</t>
+          <t>3490</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>16374</t>
+          <t>15292</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10834,7 +10834,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10849,12 +10849,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4970</t>
+          <t>4920</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>20022</t>
+          <t>20436</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10864,12 +10864,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -10892,12 +10892,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>24958</t>
+          <t>24940</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>53051</t>
+          <t>53599</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>22613</t>
+          <t>22736</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>50640</t>
+          <t>51753</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10962,12 +10962,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>54457</t>
+          <t>54645</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>94153</t>
+          <t>94095</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10977,12 +10977,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,21%</t>
         </is>
       </c>
     </row>
@@ -11005,12 +11005,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>278481</t>
+          <t>278443</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>307241</t>
+          <t>306608</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>316998</t>
+          <t>318004</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>347947</t>
+          <t>348968</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11075,12 +11075,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>606609</t>
+          <t>606368</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>648729</t>
+          <t>647821</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11090,12 +11090,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>90,97%</t>
         </is>
       </c>
     </row>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7383</t>
+          <t>7368</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>10154</t>
+          <t>10434</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11290,7 +11290,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11305,12 +11305,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1386</t>
+          <t>1415</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>11843</t>
+          <t>12161</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11320,12 +11320,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -11348,12 +11348,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9773</t>
+          <t>9630</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>26474</t>
+          <t>27705</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>30188</t>
+          <t>30169</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>64885</t>
+          <t>66240</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -11403,7 +11403,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -11418,12 +11418,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>44068</t>
+          <t>42319</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>86399</t>
+          <t>86962</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -11433,12 +11433,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,23%</t>
         </is>
       </c>
     </row>
@@ -11461,7 +11461,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>227915</t>
+          <t>226848</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -11476,7 +11476,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>332254</t>
+          <t>330988</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>367058</t>
+          <t>368002</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11531,12 +11531,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>566499</t>
+          <t>565530</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>608393</t>
+          <t>608859</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11546,12 +11546,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,65%</t>
         </is>
       </c>
     </row>
@@ -11691,12 +11691,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>178617</t>
+          <t>180086</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>241047</t>
+          <t>240430</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>202153</t>
+          <t>203796</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>259728</t>
+          <t>263276</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11761,12 +11761,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>400298</t>
+          <t>400647</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>482043</t>
+          <t>485099</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11781,7 +11781,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -11804,12 +11804,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>274204</t>
+          <t>276436</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>357739</t>
+          <t>356515</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>282727</t>
+          <t>284269</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>372028</t>
+          <t>373978</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -11874,12 +11874,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>581689</t>
+          <t>588620</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>702024</t>
+          <t>706338</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -11889,12 +11889,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,18%</t>
         </is>
       </c>
     </row>
@@ -11917,12 +11917,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2821365</t>
+          <t>2820761</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2919471</t>
+          <t>2919993</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2934563</t>
+          <t>2934752</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3040168</t>
+          <t>3036402</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -11987,12 +11987,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>5789390</t>
+          <t>5789742</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5930353</t>
+          <t>5925147</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12002,12 +12002,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,39%</t>
         </is>
       </c>
     </row>
@@ -12377,32 +12377,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3141</t>
+          <t>45774</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1862</t>
+          <t>28425</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5091</t>
+          <t>68064</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2954</t>
+          <t>36531</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1823</t>
+          <t>23186</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4577</t>
+          <t>55382</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>6096</t>
+          <t>82305</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>58465</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8548</t>
+          <t>110332</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>14,32%</t>
         </is>
       </c>
     </row>
@@ -12490,32 +12490,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15366</t>
+          <t>12658</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4119</t>
+          <t>2989</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37533</t>
+          <t>29793</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -12525,32 +12525,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8887</t>
+          <t>9475</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3155</t>
+          <t>3613</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19550</t>
+          <t>22198</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>24253</t>
+          <t>22133</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10899</t>
+          <t>10795</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>46684</t>
+          <t>41738</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -12603,32 +12603,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>381480</t>
+          <t>349360</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>359364</t>
+          <t>322929</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>392789</t>
+          <t>369577</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -12638,32 +12638,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>301359</t>
+          <t>316507</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>291036</t>
+          <t>296925</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>307666</t>
+          <t>332422</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -12673,32 +12673,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>682839</t>
+          <t>665867</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>660347</t>
+          <t>632433</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>695951</t>
+          <t>692170</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>89,86%</t>
         </is>
       </c>
     </row>
@@ -12716,17 +12716,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12751,17 +12751,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12786,17 +12786,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12833,32 +12833,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5266</t>
+          <t>49872</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3552</t>
+          <t>33462</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7418</t>
+          <t>67259</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12868,32 +12868,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>10102</t>
+          <t>66542</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7663</t>
+          <t>51371</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12955</t>
+          <t>84018</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>15369</t>
+          <t>116414</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12237</t>
+          <t>94605</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>18839</t>
+          <t>140143</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>14,36%</t>
         </is>
       </c>
     </row>
@@ -12946,32 +12946,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21917</t>
+          <t>22564</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12038</t>
+          <t>12274</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>37813</t>
+          <t>38816</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -12981,67 +12981,67 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22054</t>
+          <t>21464</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13991</t>
+          <t>13043</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33833</t>
+          <t>33193</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
+          <t>2,61%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>6,65%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>44028</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>30964</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>61642</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>4,51%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
           <t>3,17%</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>7,67%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>43971</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>31168</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>64018</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>5,09%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>3,61%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -13059,32 +13059,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>396364</t>
+          <t>404454</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>380763</t>
+          <t>381495</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>406251</t>
+          <t>423726</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -13094,32 +13094,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>408845</t>
+          <t>411300</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>397612</t>
+          <t>391077</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>417799</t>
+          <t>429702</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>78,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -13129,32 +13129,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>805208</t>
+          <t>815754</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>784784</t>
+          <t>787102</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>818553</t>
+          <t>840044</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>86,05%</t>
         </is>
       </c>
     </row>
@@ -13172,17 +13172,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -13207,17 +13207,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>441001</t>
+          <t>499306</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>441001</t>
+          <t>499306</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>441001</t>
+          <t>499306</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -13242,17 +13242,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>864548</t>
+          <t>976196</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>864548</t>
+          <t>976196</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>864548</t>
+          <t>976196</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -13289,32 +13289,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11481</t>
+          <t>79507</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8974</t>
+          <t>61252</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14510</t>
+          <t>97179</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -13324,32 +13324,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>16693</t>
+          <t>75057</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13556</t>
+          <t>62057</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20487</t>
+          <t>89405</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -13359,32 +13359,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>28173</t>
+          <t>154564</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>24455</t>
+          <t>132363</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>32997</t>
+          <t>177062</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>14,24%</t>
         </is>
       </c>
     </row>
@@ -13402,32 +13402,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>25784</t>
+          <t>25928</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16979</t>
+          <t>16828</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36641</t>
+          <t>38560</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -13437,32 +13437,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>31648</t>
+          <t>32246</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23486</t>
+          <t>23597</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42310</t>
+          <t>42320</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -13472,32 +13472,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>57432</t>
+          <t>58174</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44149</t>
+          <t>44730</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>71319</t>
+          <t>73023</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -13515,32 +13515,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>499073</t>
+          <t>515402</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>487303</t>
+          <t>494940</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>507765</t>
+          <t>535030</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -13550,32 +13550,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>494127</t>
+          <t>514836</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>484065</t>
+          <t>498369</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>503653</t>
+          <t>530832</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -13585,32 +13585,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>993200</t>
+          <t>1030238</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>978728</t>
+          <t>1004531</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1006956</t>
+          <t>1054463</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>84,83%</t>
         </is>
       </c>
     </row>
@@ -13628,17 +13628,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -13663,17 +13663,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -13698,17 +13698,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -13745,32 +13745,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>8216</t>
+          <t>54987</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5964</t>
+          <t>41201</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11102</t>
+          <t>72781</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13780,32 +13780,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>14199</t>
+          <t>56361</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11554</t>
+          <t>44940</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17862</t>
+          <t>67443</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13815,32 +13815,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>22416</t>
+          <t>111349</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18837</t>
+          <t>94242</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26500</t>
+          <t>131353</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>9,18%</t>
         </is>
       </c>
     </row>
@@ -13858,32 +13858,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>44093</t>
+          <t>43996</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32474</t>
+          <t>31336</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>58876</t>
+          <t>58178</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13893,32 +13893,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>35110</t>
+          <t>35508</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26925</t>
+          <t>27331</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>45681</t>
+          <t>45587</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13928,32 +13928,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>79202</t>
+          <t>79504</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>65510</t>
+          <t>65133</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>95237</t>
+          <t>98392</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -13971,32 +13971,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>581836</t>
+          <t>599311</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>566933</t>
+          <t>576706</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>593948</t>
+          <t>617411</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -14006,32 +14006,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>620735</t>
+          <t>640485</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>610077</t>
+          <t>623199</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>629422</t>
+          <t>654292</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -14041,32 +14041,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1202571</t>
+          <t>1239796</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1186102</t>
+          <t>1215991</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1217015</t>
+          <t>1263046</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>88,28%</t>
         </is>
       </c>
     </row>
@@ -14084,17 +14084,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>634145</t>
+          <t>698294</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>634145</t>
+          <t>698294</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>634145</t>
+          <t>698294</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -14119,17 +14119,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>670044</t>
+          <t>732354</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>670044</t>
+          <t>732354</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>670044</t>
+          <t>732354</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -14154,17 +14154,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1304189</t>
+          <t>1430649</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1304189</t>
+          <t>1430649</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1304189</t>
+          <t>1430649</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -14201,32 +14201,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>7341</t>
+          <t>43410</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5386</t>
+          <t>32058</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9806</t>
+          <t>58152</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -14236,32 +14236,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>9351</t>
+          <t>36287</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7242</t>
+          <t>27965</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12023</t>
+          <t>46160</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -14271,32 +14271,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>16693</t>
+          <t>79697</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>13896</t>
+          <t>64065</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20330</t>
+          <t>95973</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -14314,32 +14314,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>32872</t>
+          <t>32864</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>23272</t>
+          <t>23209</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>44841</t>
+          <t>46126</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -14349,32 +14349,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>25784</t>
+          <t>26962</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>18694</t>
+          <t>19477</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>34111</t>
+          <t>35534</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -14384,32 +14384,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>58656</t>
+          <t>59826</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>46099</t>
+          <t>46977</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>71717</t>
+          <t>74246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -14427,32 +14427,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>521020</t>
+          <t>533071</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>508838</t>
+          <t>515274</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>530091</t>
+          <t>548623</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -14462,32 +14462,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>510019</t>
+          <t>544447</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>501307</t>
+          <t>533050</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>517873</t>
+          <t>556475</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -14497,32 +14497,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1031039</t>
+          <t>1077519</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1017394</t>
+          <t>1055164</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1043654</t>
+          <t>1097326</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>90,16%</t>
         </is>
       </c>
     </row>
@@ -14540,17 +14540,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -14575,17 +14575,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>545155</t>
+          <t>607696</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>545155</t>
+          <t>607696</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>545155</t>
+          <t>607696</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -14610,17 +14610,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1106388</t>
+          <t>1217042</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1106388</t>
+          <t>1217042</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1106388</t>
+          <t>1217042</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -14657,32 +14657,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3265</t>
+          <t>16461</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1929</t>
+          <t>10238</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4907</t>
+          <t>24053</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -14692,32 +14692,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4176</t>
+          <t>14975</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>9777</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6020</t>
+          <t>21451</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14727,32 +14727,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>7442</t>
+          <t>31436</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5573</t>
+          <t>22890</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>9835</t>
+          <t>42497</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -14770,32 +14770,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>24180</t>
+          <t>26067</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>16768</t>
+          <t>18669</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>33063</t>
+          <t>35462</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14805,67 +14805,67 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>26133</t>
+          <t>27663</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>20093</t>
+          <t>21058</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>34873</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
+          <t>4,82%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>8,27%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>53731</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>42351</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>66425</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>6,36%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>5,02%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>8,72%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>50313</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>40336</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>61281</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>6,55%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>5,25%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -14883,32 +14883,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>340720</t>
+          <t>364552</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>331747</t>
+          <t>353714</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>348169</t>
+          <t>374165</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14918,32 +14918,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>369697</t>
+          <t>394618</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>360835</t>
+          <t>384777</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>376175</t>
+          <t>402864</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14953,32 +14953,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>710418</t>
+          <t>759170</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>698352</t>
+          <t>743444</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>720365</t>
+          <t>773109</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>91,56%</t>
         </is>
       </c>
     </row>
@@ -14996,17 +14996,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -15031,17 +15031,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>400007</t>
+          <t>437257</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>400007</t>
+          <t>437257</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>400007</t>
+          <t>437257</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -15066,17 +15066,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>768173</t>
+          <t>844337</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>768173</t>
+          <t>844337</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>768173</t>
+          <t>844337</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -15113,32 +15113,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>8133</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>4368</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3167</t>
+          <t>13911</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -15148,32 +15148,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>9158</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1442</t>
+          <t>5392</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3863</t>
+          <t>14464</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -15183,32 +15183,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>4199</t>
+          <t>17291</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2760</t>
+          <t>11994</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6021</t>
+          <t>24699</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -15226,32 +15226,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>15191</t>
+          <t>16543</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9907</t>
+          <t>10597</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>22307</t>
+          <t>24779</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -15261,32 +15261,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>20599</t>
+          <t>22445</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>14563</t>
+          <t>16682</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>27314</t>
+          <t>30808</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -15296,22 +15296,22 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>35790</t>
+          <t>38988</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>27174</t>
+          <t>29708</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>45488</t>
+          <t>49651</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
@@ -15321,7 +15321,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,42%</t>
         </is>
       </c>
     </row>
@@ -15339,32 +15339,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>265777</t>
+          <t>285523</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>258737</t>
+          <t>276827</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>271125</t>
+          <t>293060</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -15374,32 +15374,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>401908</t>
+          <t>432067</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>395094</t>
+          <t>423047</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>407857</t>
+          <t>439377</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -15409,32 +15409,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>667685</t>
+          <t>717589</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>657770</t>
+          <t>705751</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>676529</t>
+          <t>728659</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>94,16%</t>
         </is>
       </c>
     </row>
@@ -15452,17 +15452,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -15487,17 +15487,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>424915</t>
+          <t>463670</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>424915</t>
+          <t>463670</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>424915</t>
+          <t>463670</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -15522,17 +15522,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>707674</t>
+          <t>773868</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>707674</t>
+          <t>773868</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>707674</t>
+          <t>773868</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -15569,32 +15569,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>40502</t>
+          <t>298144</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>35406</t>
+          <t>261074</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>45613</t>
+          <t>337464</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -15604,32 +15604,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>59884</t>
+          <t>294912</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>53601</t>
+          <t>265536</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>66061</t>
+          <t>328000</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -15639,32 +15639,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>100386</t>
+          <t>593056</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>92570</t>
+          <t>543058</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>108929</t>
+          <t>646321</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>8,91%</t>
         </is>
       </c>
     </row>
@@ -15682,67 +15682,67 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>179403</t>
+          <t>180621</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>151383</t>
+          <t>154093</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>211277</t>
+          <t>210329</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
+          <t>4,36%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>5,96%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>175763</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>155269</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>201250</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
           <t>4,72%</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>6,59%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>170215</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>150137</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>192495</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>5,1%</t>
-        </is>
-      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -15752,32 +15752,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>349618</t>
+          <t>356384</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>315783</t>
+          <t>319941</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>391168</t>
+          <t>395752</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -15795,32 +15795,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>2986271</t>
+          <t>3051674</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2954503</t>
+          <t>3003363</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3013607</t>
+          <t>3095472</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -15830,32 +15830,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>3106690</t>
+          <t>3254260</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>3082487</t>
+          <t>3215621</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3128547</t>
+          <t>3292061</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -15865,32 +15865,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>6092961</t>
+          <t>6305933</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>6048659</t>
+          <t>6240182</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6126963</t>
+          <t>6365423</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>87,73%</t>
         </is>
       </c>
     </row>
@@ -15908,17 +15908,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>3206176</t>
+          <t>3530439</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3206176</t>
+          <t>3530439</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3206176</t>
+          <t>3530439</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -15943,17 +15943,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>3336790</t>
+          <t>3724935</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3336790</t>
+          <t>3724935</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3336790</t>
+          <t>3724935</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -15978,17 +15978,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>6542966</t>
+          <t>7255373</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>6542966</t>
+          <t>7255373</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>6542966</t>
+          <t>7255373</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
